--- a/Assets/Data/Dungeon1020.xlsx
+++ b/Assets/Data/Dungeon1020.xlsx
@@ -93,10 +93,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -114,9 +114,106 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -139,7 +236,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -148,104 +245,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,7 +273,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,7 +351,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +381,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,13 +399,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,61 +429,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,61 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,26 +491,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -533,8 +518,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -546,6 +531,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -566,7 +566,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -575,13 +575,13 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -590,121 +590,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon1020.xlsx
+++ b/Assets/Data/Dungeon1020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -55,10 +55,10 @@
     <t>Tr:D1</t>
   </si>
   <si>
-    <t>Tr:D3</t>
+    <t>Out</t>
   </si>
   <si>
-    <t>Out</t>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -93,10 +93,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -114,16 +114,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -143,23 +150,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -173,30 +173,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -208,6 +201,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -227,8 +235,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -237,22 +252,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,6 +273,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -285,7 +291,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,13 +303,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,7 +315,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,7 +339,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,7 +357,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,13 +369,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,31 +399,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,31 +429,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,7 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,21 +500,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -558,6 +543,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -566,22 +566,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -590,121 +590,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -784,19 +784,17 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
+      <sheetName val="StageEvents"/>
+      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1011,6 +1009,8 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1730,7 +1730,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>9</v>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
@@ -2283,11 +2283,11 @@
         <v>9</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>9</v>
@@ -3897,7 +3897,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>9</v>
@@ -4165,7 +4165,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>9</v>
